--- a/output/gpu_prices_2026-06-12.xlsx
+++ b/output/gpu_prices_2026-06-12.xlsx
@@ -19,16 +19,13 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <b val="1"/>
@@ -53,7 +50,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -61,24 +58,16 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">

--- a/output/gpu_prices_2026-06-12.xlsx
+++ b/output/gpu_prices_2026-06-12.xlsx
@@ -997,7 +997,7 @@
       <c r="K21" s="3" t="inlineStr"/>
       <c r="L21" s="3" t="inlineStr"/>
       <c r="M21" s="3" t="n">
-        <v>0.19</v>
+        <v>0.21</v>
       </c>
       <c r="N21" s="3" t="inlineStr"/>
     </row>
